--- a/content/tz-hskk-2.xlsx
+++ b/content/tz-hskk-2.xlsx
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>На среднем уровне HSKK повторять за диктором уже мало: появляется 看图说话 — рассказ по картинке. Разбираем, что меняется после HSKK 1, как за минуту собрать план ответа по картинке, какие грамматические связки держат речь и что делать, если мысль кончилась, а время ещё осталось.</t>
+          <t>HSKK 2 — средний уровень устного экзамена: здесь уже мало повторять за диктором, нужно самому рассказать, что происходит на картинке. Объясняем, чем этот уровень отличается от HSKK 1, как по простой схеме собрать рассказ из четырёх предложений, какие связки не дают замолчать и чем дотянуть ответ до конца записи.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Что меняется после HSKK 1, как собрать план ответа по картинке за минуту и чем дотянуть рассказ, если мысль кончилась раньше времени.</t>
+          <t>Чем средний уровень отличается от начального, как собрать рассказ по картинке из четырёх предложений и чем дотянуть ответ до конца записи.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
